--- a/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:58:57+00:00</t>
+    <t>2026-05-05T16:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T16:17:29+00:00</t>
+    <t>2026-05-06T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T12:21:18+00:00</t>
+    <t>2026-05-27T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
+++ b/cp-card-custodian/ig/StructureDefinition-pdsm-folder-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:29:51+00:00</t>
+    <t>2026-05-28T14:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
